--- a/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T06:56:43+00:00</t>
+    <t>2026-05-06T06:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T06:58:56+00:00</t>
+    <t>2026-05-06T09:08:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T09:08:16+00:00</t>
+    <t>2026-05-06T11:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:48:14+00:00</t>
+    <t>2026-05-06T11:59:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:59:43+00:00</t>
+    <t>2026-05-06T16:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
+++ b/feature/fix-juridiction/ig/StructureDefinition-FrScheduleAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T16:23:13+00:00</t>
+    <t>2026-05-07T08:01:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
